--- a/data/trans_dic/P37A$otros-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P37A$otros-Provincia-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
     </row>
@@ -717,47 +717,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,61</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,02</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,74</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,09</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,9</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,38</t>
+          <t>0,13; 1,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,41</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -857,27 +857,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,47</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,67</t>
+          <t>1,85; 5,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,88</t>
+          <t>2,52; 5,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,88</t>
+          <t>0,09; 0,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,97</t>
+          <t>2,5; 4,86</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,32</t>
+          <t>0,26; 2,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
+          <t>0,13; 1,21</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
           <t>0,14; 1,19</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,13; 1,18</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,32</t>
+          <t>0,22; 3,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,27</t>
+          <t>0,42; 2,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,17 +1162,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,48</t>
+          <t>0,26; 2,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,53</t>
+          <t>0,23; 2,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,53</t>
+          <t>0,48; 2,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,34</t>
+          <t>0,14; 1,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,11</t>
+          <t>0,33; 2,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,17</t>
+          <t>0,67; 2,34</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,25</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,84</t>
+          <t>0,32; 1,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,17 +1582,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,15</t>
+          <t>0,13; 1,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,92</t>
+          <t>0,57; 2,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1602,17 +1602,17 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,55</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,03</t>
+          <t>0,16; 0,97</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,55</t>
+          <t>0,64; 1,95</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,61</t>
+          <t>0,05; 0,55</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,32</t>
+          <t>0,0; 0,42</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,55</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1837,27 +1837,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,26</t>
+          <t>0,03; 0,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,22</t>
+          <t>0,0; 0,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,71</t>
+          <t>0,2; 0,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,28</t>
+          <t>0,62; 1,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,3</t>
+          <t>0,03; 0,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1867,32 +1867,32 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,57</t>
+          <t>0,17; 0,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,29</t>
+          <t>0,78; 1,48</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,23</t>
+          <t>0,06; 0,24</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,2</t>
+          <t>0,05; 0,23</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,52</t>
+          <t>0,22; 0,53</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,18</t>
+          <t>0,77; 1,26</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>641</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>641</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4742</t>
+          <t>0; 4396</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6144</t>
+          <t>0; 5919</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2239,17 +2239,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5482</t>
+          <t>0; 5031</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3381</t>
+          <t>0; 3044</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4645</t>
+          <t>0; 4385</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>785; 8054</t>
+          <t>785; 7393</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3406</t>
+          <t>0; 2626</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16219</t>
+          <t>17264</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20231</t>
+          <t>20382</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36450</t>
+          <t>37646</t>
         </is>
       </c>
     </row>
@@ -2417,27 +2417,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5358</t>
+          <t>0; 6485</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6071</t>
+          <t>0; 6763</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7378</t>
+          <t>0; 7351</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8371; 29409</t>
+          <t>9797; 28673</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6570</t>
+          <t>0; 7183</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2452,27 +2452,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13741; 30286</t>
+          <t>13797; 29259</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>874; 8813</t>
+          <t>881; 7539</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6707</t>
+          <t>0; 5828</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 7909</t>
+          <t>0; 7547</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26145; 51315</t>
+          <t>26904; 52349</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3111</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 6096</t>
+          <t>0; 6564</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2655,12 +2655,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>889; 7810</t>
+          <t>873; 7436</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4196</t>
+          <t>0; 4476</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2675,12 +2675,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>888; 7791</t>
+          <t>882; 7928</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>867; 7822</t>
+          <t>924; 8010</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>9802</t>
         </is>
       </c>
     </row>
@@ -2843,12 +2843,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>845; 12288</t>
+          <t>828; 11912</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1649; 10205</t>
+          <t>1580; 10512</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2858,17 +2858,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1014; 9638</t>
+          <t>1024; 10379</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>883; 9799</t>
+          <t>887; 9411</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1752; 12058</t>
+          <t>2021; 12537</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2878,17 +2878,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1016; 10239</t>
+          <t>1033; 10135</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2562; 15979</t>
+          <t>2470; 15755</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4548; 17126</t>
+          <t>5305; 18607</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1167</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4366</t>
+          <t>0; 4905</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3759</t>
+          <t>0; 4095</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4382</t>
+          <t>0; 4986</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 4454</t>
+          <t>0; 4236</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>648</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>648</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3279,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 7248</t>
+          <t>0; 7868</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3201</t>
+          <t>0; 4285</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 7225</t>
+          <t>0; 8684</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 4132</t>
+          <t>0; 3308</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>16130</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1055; 10129</t>
+          <t>1059; 10117</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1920; 11503</t>
+          <t>2276; 13720</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,17 +3482,17 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 6273</t>
+          <t>0; 6187</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>915; 7960</t>
+          <t>922; 8110</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1667; 16327</t>
+          <t>4411; 21251</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3502,17 +3502,17 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 5832</t>
+          <t>0; 7447</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2922; 13867</t>
+          <t>2147; 13028</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5608; 22766</t>
+          <t>9534; 29025</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2889</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 5727</t>
+          <t>0; 5893</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3675,17 +3675,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 5331</t>
+          <t>0; 6659</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 9287</t>
+          <t>0; 10783</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 7879</t>
+          <t>0; 8598</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>772; 9293</t>
+          <t>769; 8476</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 5137</t>
+          <t>0; 6739</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 8983</t>
+          <t>0; 8872</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30299</t>
+          <t>32872</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>34830</t>
+          <t>39162</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>65128</t>
+          <t>72034</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>880; 8415</t>
+          <t>876; 8839</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 7488</t>
+          <t>0; 6756</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6929; 23930</t>
+          <t>6729; 23249</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19346; 44262</t>
+          <t>22044; 47690</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>986; 10156</t>
+          <t>984; 10786</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1951; 11884</t>
+          <t>1950; 11838</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5934; 20233</t>
+          <t>5963; 20430</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>24327; 47813</t>
+          <t>29078; 55356</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3806; 15158</t>
+          <t>3725; 15682</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3000; 14019</t>
+          <t>3192; 15800</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15227; 36172</t>
+          <t>15150; 36591</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>49201; 84626</t>
+          <t>56208; 91698</t>
         </is>
       </c>
     </row>
